--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35377-2026 artfynd.xlsx
+++ b/artfynd/A 35377-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048897</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048896</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136048898</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
